--- a/utils/data-room-simulator/output/department_summary.xlsx
+++ b/utils/data-room-simulator/output/department_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Departments" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>headcount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>total_salary</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>avg_salary</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>min_salary</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max_salary</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_of_total</t>
         </is>
@@ -472,22 +460,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>17242075.47</v>
+        <v>8374259.81</v>
       </c>
       <c r="D2" t="n">
-        <v>246315.3638571428</v>
+        <v>126882.7243939394</v>
       </c>
       <c r="E2" t="n">
-        <v>118857.58</v>
+        <v>65343.63</v>
       </c>
       <c r="F2" t="n">
-        <v>437118.62</v>
+        <v>237235.76</v>
       </c>
       <c r="G2" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="3">
@@ -497,19 +485,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>8002992.8</v>
+        <v>4278309.29</v>
       </c>
       <c r="D3" t="n">
-        <v>160059.856</v>
+        <v>91027.85723404256</v>
       </c>
       <c r="E3" t="n">
-        <v>77212.44</v>
+        <v>44102.63</v>
       </c>
       <c r="F3" t="n">
-        <v>413808.34</v>
+        <v>225085.05</v>
       </c>
       <c r="G3" t="n">
         <v>25.3</v>
@@ -522,72 +510,72 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>4261497.55</v>
+        <v>2072139.25</v>
       </c>
       <c r="D4" t="n">
-        <v>142049.9183333333</v>
+        <v>74004.97321428571</v>
       </c>
       <c r="E4" t="n">
-        <v>67508.94</v>
+        <v>40902.24</v>
       </c>
       <c r="F4" t="n">
-        <v>222804.71</v>
+        <v>128378.04</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>G&amp;A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>2979026.08</v>
+        <v>1226155.59</v>
       </c>
       <c r="D5" t="n">
-        <v>148951.304</v>
+        <v>68119.755</v>
       </c>
       <c r="E5" t="n">
-        <v>71642.98</v>
+        <v>32843.16</v>
       </c>
       <c r="F5" t="n">
-        <v>321340.77</v>
+        <v>242543.77</v>
       </c>
       <c r="G5" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>2148483.4</v>
+        <v>1442027.17</v>
       </c>
       <c r="D6" t="n">
-        <v>113078.0736842105</v>
+        <v>80112.62055555555</v>
       </c>
       <c r="E6" t="n">
-        <v>64326.01</v>
+        <v>42244.61</v>
       </c>
       <c r="F6" t="n">
-        <v>404933.81</v>
+        <v>119407.47</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -600,19 +588,19 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>2332340.53</v>
+        <v>1466132.98</v>
       </c>
       <c r="D7" t="n">
-        <v>259148.9477777778</v>
+        <v>162903.6644444444</v>
       </c>
       <c r="E7" t="n">
-        <v>178695.95</v>
+        <v>105002.86</v>
       </c>
       <c r="F7" t="n">
-        <v>379372.96</v>
+        <v>223263.63</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>
